--- a/rtm_inputs.xlsx
+++ b/rtm_inputs.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strata" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frame" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cells" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefixes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Files" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frame" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cells" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefixes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Files" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,12 +38,12 @@
       <sz val="14"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
     </font>
   </fonts>
   <fills count="4">
@@ -75,17 +76,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8D7DA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -447,211 +460,215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>rtmtools input workbook (schema rtm-input-1.0)</t>
+          <t>Start here</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fill in this workbook, then in Stata:  rtminput using rtm_inputs.xlsx, check   (validates every sheet and writes a Checks sheet into a copy)</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Answer the four questions, then fill only the sheets they point to. Then in Stata: User &gt; RTM tools &gt; Start here, and click the steps.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                      rtminput using rtm_inputs.xlsx, sampling   (size, frame check, allocation, draw, second stage, phone subsample)</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                      rtminput using rtm_inputs.xlsx, weights round(1)   (base, nonresponse, trim, calibrate, report for that round)</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1. Do you have a list of areas (enumeration areas, villages, blocks) with the number of households in each?</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A folder of CSV files named design.csv, strata.csv, frame.csv, totals.csv, cells.csv, prefixes.csv, files.csv works the same (rtminput using folder/).</t>
+          <t xml:space="preserve">   Yes</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Paste it into the Frame sheet (area_id, stratum_id, size_hh; one row per area) and list the strata on the Strata sheet. On Design, set n_areas, allocation, stage1, reserve_areas.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   No, only boundaries and a population map</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Build the area frame first with rtmframe grid (User &gt; RTM tools &gt; Frame &gt; Grid frame...), save it, then paste it into Frame with x and y and set stage1 to grid.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Design: one row per setting (key, value). Blank = the default, whose source is in the note column. Rows whose key starts with # are headings.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   No frame at all, phone numbers only</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Fill the Prefixes sheet (one row per operator prefix) and set rdd to yes on Design; leave Frame empty.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Strata: one row per stratum (stratum_id, label, population_hh, population_persons). stratum_id must match Frame.</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Frame: one row per area (area_id, stratum_id, size_hh required; size_persons, x, y, exclude and any sorting columns optional).</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2. How will the households inside each selected area be chosen?</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Totals: one row per category for calibration (variable, level, total), as the Stata command rtmweight calibrate reads it.</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   From a household list you already have</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Add a household_list row on the Files sheet (path, id, area_id) and set households_per_area on Design.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Cells: one row per census cell for cell post-stratification (the cell variables, then total).</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   From a field listing done after the areas are drawn</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Run the sampling once for the areas, list them in the field, then add a listing row on Files and run the sampling again.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Prefixes: one row per operator prefix for random digit dialing (prefix, n_numbers, digits).</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Not needed (areas only, or phone numbers)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Leave households_per_area blank.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Files: one row per household-level data file (baseline, round, household_list, listing) with the names of its key variables. The data stay in those files.</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>3. Is there a baseline survey whose households you will call?</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>The example rows are the package's synthetic data: nothing here is a real household. Replace every sheet with your program's inputs.</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Yes</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Add a baseline row on Files (path, id, psu, strata, weight, phone) and set phone_per_psu on Design: that many per PSU are called first, the rest are ordered replacements.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Nothing in this workbook is a design recommendation: the choices are yours, and each default's source is named so you can check it.</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   No</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Leave phone_per_psu blank; the weights then start from the sample's own probabilities (base_weight probabilities).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Column headings shaded yellow are required; the others may stay empty. Do not rename the sheets or the heading row.</t>
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>4. Are you weighting a round of phone interviews now?</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Files sheet columns</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Yes</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Add a round row on Files (path, id, response = the 1/0 interviewed column, round number). On Design choose nonresponse (and its covariates, classes or cells), trim and calibrate; fill Totals if you calibrate, Cells if you post-stratify.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>role: baseline | round | household_list | listing</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Not yet</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Skip the weights rows; they can be filled when the first round is in.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>path: file path, relative to this workbook's folder or absolute (.dta, .csv or .xlsx)</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>id: household identifier (baseline, round, household_list)</t>
+          <t>Then</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>response: round: the 0/1 response indicator of that round</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   In Stata: User &gt; RTM tools &gt; Start here. Step 2 checks this workbook and lists every problem with its sheet, row and column; step 3 draws the sample; step 4 weights a round.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>psu: baseline: the PSU variable (the phone subsample is drawn within it)</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Each step opens a plain-language summary of what it did and where the files are.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>strata: baseline: the stratum variable (by-groups of the base weight and of the report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>weight: baseline: the baseline weight (base_weight baseline)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>probabilities: baseline: the stage inclusion probabilities, space separated (base_weight probabilities)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>phone: baseline: 1 = household in the phone sample (blank: every household)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>area_id: household_list or listing: the area identifier that matches Frame area_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>round: round: the round number</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>note: free text</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The example rows are the package's synthetic data, so every step runs as shipped; replace them with your own.</t>
         </is>
       </c>
     </row>
@@ -666,819 +683,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rtmtools input workbook (schema rtm-input-1.0)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t># project</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fill in this workbook, then in Stata:  rtminput using rtm_inputs.xlsx, check   (validates every sheet and writes a Checks sheet into a copy)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RTM synthetic example</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>free text: the program's name, written into the exports</t>
+          <t xml:space="preserve">                                      rtminput using rtm_inputs.xlsx, sampling   (size, frame check, allocation, draw, second stage, phone subsample)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>20261024</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>integer; the same seed repeats every draw; blank: Stata draws one and records it</t>
+          <t xml:space="preserve">                                      rtminput using rtm_inputs.xlsx, weights round(1)   (base, nonresponse, trim, calibrate, report for that round)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>output_dir</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>rtm_outputs</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>folder for the output files, relative to the folder you run Stata from</t>
+          <t>A folder of CSV files named design.csv, strata.csv, frame.csv, totals.csv, cells.csv, prefixes.csv, files.csv works the same (rtminput using folder/).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t># sample size (rtmsample size)</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>level | change: what the sample size is set for</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Design: one row per setting (key, value). Blank = the default, whose source is in the note column. Rows whose key starts with # are headings.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>expected proportion of the key indicator (UN 2008 para 59)</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Strata: one row per stratum (stratum_id, label, population_hh, population_persons). stratum_id must match Frame.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>relmargin</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>relative margin of error at 95 percent (UN 2008 para 59: 10 percent); or set margin below</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Frame: one row per area (area_id, stratum_id, size_hh required; size_persons, x, y, exclude and any sorting columns optional).</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>absolute margin instead of relmargin</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Totals: one row per category for calibration (variable, level, total), as the Stata command rtmweight calibrate reads it.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>change</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>with target change: the change to detect, for example -0.05</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cells: one row per census cell for cell post-stratification (the cell variables, then total).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>power</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>with target change: power of the test</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Prefixes: one row per operator prefix for random digit dialing (prefix, n_numbers, digits).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>deff</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>design effect (UN 2008 para 60: about 2 for clustered samples, about 1 for a list sample)</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Files: one row per household-level data file (baseline, round, household_list, listing) with the names of its key variables. The data stay in those files.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>nonresponse_mult</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>nonresponse multiplier (UN 2008 para 60)</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>attrition</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.015</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>attrition per round of the panel (MPPS 2016 p. 45); 0 = none</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>The example rows are the package's synthetic data: nothing here is a real household. Replace every sheet with your program's inputs.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rounds</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>rounds of the panel</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Nothing in this workbook is a design recommendation: the choices are yours, and each default's source is named so you can check it.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>firstloss</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>loss between the baseline and the first phone round; 0 = none</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>domains</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>domains that need equal reliability</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Column headings shaded yellow are required; the others may stay empty. Do not rename the sheets or the heading row.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t># frame check and allocation (rtmframe list, rtmsample allocate)</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Files sheet columns</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>minsize</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>areas with fewer households are flagged (GM 1996 pp. 78-79: appended to a neighbour); 0 = none</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>role: baseline | round | household_list | listing</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>maxsize</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>areas with more are flagged for segmentation (UN 2008 paras 138-140); 0 = none</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>path: file path, relative to this workbook's folder or absolute (.dta, .csv or .xlsx)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>n_areas</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>areas to select in total (required for sampling)</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>id: household identifier (baseline, round, household_list)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>allocation</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>proportional</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>proportional | equal | neyman | power (UN 2008 paras 68-70; Cochran 1977 5.5; Bankier 1988)</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>response: round: the 0/1 response indicator of that round</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>power_q</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>exponent of power allocation</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>psu: baseline: the PSU variable (the phone subsample is drawn within it)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>min_areas</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>minimum areas per stratum; 0 = none</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>strata: baseline: the stratum variable (by-groups of the base weight and of the report)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>max_areas</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>maximum areas per stratum; 0 = none</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>weight: baseline: the baseline weight (base_weight baseline)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t># first stage (rtmsample draw or rtmsample grid)</t>
+          <t>probabilities: baseline: the stage inclusion probabilities, space separated (base_weight probabilities)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>stage1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ppssys</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>ppssys | pps | systematic | srs | grid (UN 2008 paras 77-79 and 118-119; grid = serpentine order, needs x y)</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>phone: baseline: 1 = household in the phone sample (blank: every household)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sort_vars</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>stratum_id area_id</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Frame columns that give the geographic order within strata (implicit stratification)</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>area_id: household_list or listing: the area identifier that matches Frame area_id</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>reserve_areas</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>reserve areas per stratum: a number, all, or 0 (UN 2008 paras 172, 178-179)</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>round: round: the round number</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t># second stage (rtmsample draw within the selected areas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>households_per_area</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>households per selected area, from the household_list or listing file of the Files sheet; blank = no second stage</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t># phone subsample of a baseline (rtmsample draw, reserve all)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>phone_per_psu</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>households per PSU called first, every other household an ordered replacement; blank = none (needs a baseline row in Files)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t># random digit dialing (rtmsample rdd)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>rdd</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>yes | no: draw numbers from the Prefixes sheet; the numbers are never exported</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t># weights of a round (rtmweight base, nonresponse, trim, calibrate, report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>base_weight</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>baseline</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>baseline | probabilities: the baseline weight redistributed to the phone sample, or 1 / product of the probabilities (HFPS Vol. 2 pp. 10-11, 21)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>nonresponse</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>propensity</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>propensity | probit | classes | ebalance | ebalance_nobase | post | none (HFPS Vol. 2 Annex A2.3.1: propensity in deciles; ebalance and post are L2 program practice)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>covariates</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>urban i.educ head_age assets hhsize</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>baseline variables of the propensity model or of the balancing (i. for categories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>classes</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>region urban</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>class variables for nonresponse classes (UN 2008 section 6.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>region urban head_female agegrp</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>cell variables for nonresponse post: the columns of the Cells sheet before total</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ngroups</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>propensity groups (deciles)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>moments</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>balancing moments: 1 means, 2 adds variances, 3 adds skewness</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>none | winsor | cap (HFPS Vol. 2 p. 11 winsorises at the 98th percentile; UN 2008 section 6.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>trim_pct</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>winsorising percentile</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>trim_cap</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>absolute cap for trim cap, or blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>trim_capmult</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>cap as a multiple of the median, or blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>calibrate</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>rake</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>none | rake | regress | post (Deville and Sarndal 1992; Deville, Sarndal and Sautory 1993)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cal_vars</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>region urban</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>categorical variables to calibrate on; every category must be on the Totals sheet; blank = every variable there</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cal_ll</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>lower bound on the weight ratio (regress), or blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cal_ul</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>upper bound, or blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>report_by</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>variable for the by-group table of the weighting report, or blank</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>report_files</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>yes | no: write the Word method note and the Excel report into output_dir</t>
+          <t>note: free text</t>
         </is>
       </c>
     </row>
@@ -1488,6 +897,1217 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="110" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t># project</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RTM synthetic example</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>What is the program called?</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. free text: the program's name, written into the exports</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20261024</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Which seed should every draw use (any whole number; keep it to repeat the draw)?</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. integer; the same seed repeats every draw; blank: Stata draws one and records it</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>output_dir</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rtm_outputs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Which folder should the outputs go to?</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: rtm_outputs. folder for the output files, relative to the folder you run Stata from</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t># sample size (rtmsample size)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>sample size (rtmsample size)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Is the sample sized to measure a level, or to detect a change?</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: level. level | change: what the sample size is set for</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What share do you expect for the key indicator (0 to 1)?</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. expected proportion of the key indicator (UN 2008 para 59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>relmargin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How precise, as a relative margin of error (0.10 = plus or minus 10 percent of the share)?</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. relative margin of error at 95 percent (UN 2008 para 59: 10 percent); or set margin below</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Or as an absolute margin (0.03 = plus or minus 3 points)?</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. absolute margin instead of relmargin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>If a change: how large a change should be detected (-0.05 = a fall of 5 points)?</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. with target change: the change to detect, for example -0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>If a change: with what power (0.8 is usual)?</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 0.8 (command). with target change: power of the test</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>deff</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How clustered is the sample (design effect; 2 for areas then households, 1 for a list)?</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 2 (command). design effect (UN 2008 para 60: about 2 for clustered samples, about 1 for a list sample)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>nonresponse_mult</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How much to inflate for nonresponse (1.1 = 10 percent more)?</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 1.1 (command). nonresponse multiplier (UN 2008 para 60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>attrition</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What share of the panel is lost each round (0.015 = 1.5 percent)?</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. attrition per round of the panel (MPPS 2016 p. 45); 0 = none</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rounds</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>How many rounds will the panel run?</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. rounds of the panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>firstloss</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>What share is lost between the baseline and the first phone round?</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. loss between the baseline and the first phone round; 0 = none</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>domains</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>For how many domains (regions, groups) is this precision needed?</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. domains that need equal reliability</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t># frame check and allocation (rtmframe list, rtmsample allocate)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>frame check and allocation (rtmframe list, rtmsample allocate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>minsize</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Below how many households is an area too small to sample alone (0 = no check)?</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 0. areas with fewer households are flagged (GM 1996 pp. 78-79: appended to a neighbour); 0 = none</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>maxsize</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Above how many households should an area be listed in segments (0 = no check)?</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 0. areas with more are flagged for segmentation (UN 2008 paras 138-140); 0 = none</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>n_areas</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>How many areas should be selected in total?</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. areas to select in total (required for sampling)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>allocation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>proportional</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>How should the areas be spread across strata?</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: proportional. proportional | equal | neyman | power (UN 2008 paras 68-70; Cochran 1977 5.5; Bankier 1988)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>power_q</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>If power allocation: which exponent (0.5 is usual)?</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 0.5 (command). exponent of power allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>min_areas</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>At least how many areas per stratum (0 = no minimum)?</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 0. minimum areas per stratum; 0 = none</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>max_areas</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>At most how many areas per stratum (0 = no maximum)?</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 0. maximum areas per stratum; 0 = none</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t># first stage (rtmsample draw or rtmsample grid)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>first stage (rtmsample draw or rtmsample grid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>stage1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ppssys</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>How should the areas be drawn?</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: ppssys. ppssys | pps | systematic | srs | grid (UN 2008 paras 77-79 and 118-119; grid = serpentine order, needs x y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sort_vars</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>stratum_id area_id</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Which Frame columns give the geographic order within strata (spread the sample)?</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. Frame columns that give the geographic order within strata (implicit stratification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>reserve_areas</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>How many reserve areas per stratum (a number, all, or 0)?</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 2. reserve areas per stratum: a number, all, or 0 (UN 2008 paras 172, 178-179)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t># second stage (rtmsample draw within the selected areas)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>second stage (rtmsample draw within the selected areas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>households_per_area</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>How many households per selected area (blank = none; needs a household list or listing on Files)?</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. households per selected area, from the household_list or listing file of the Files sheet; blank = no second stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t># phone subsample of a baseline (rtmsample draw, reserve all)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>phone subsample of a baseline (rtmsample draw, reserve all)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>phone_per_psu</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>How many households per PSU are called first (blank = no phone subsample; needs a baseline on Files)?</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. households per PSU called first, every other household an ordered replacement; blank = none (needs a baseline row in Files)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t># random digit dialing (rtmsample rdd)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>random digit dialing (rtmsample rdd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>rdd</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Should phone numbers be generated from operator prefixes (random digit dialing)?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: no. yes | no: draw numbers from the Prefixes sheet; the numbers are never exported</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t># weights of a round (rtmweight base, nonresponse, trim, calibrate, report)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>weights of a round (rtmweight base, nonresponse, trim, calibrate, report)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>base_weight</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Where does the base weight come from?</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: baseline. baseline | probabilities: the baseline weight redistributed to the phone sample, or 1 / product of the probabilities (HFPS Vol. 2 pp. 10-11, 21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>nonresponse</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>propensity</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>How should the weights be adjusted for households not interviewed?</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: propensity. propensity | probit | classes | ebalance | ebalance_nobase | post | none (HFPS Vol. 2 Annex A2.3.1: propensity in deciles; ebalance and post are L2 program practice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>covariates</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>urban i.educ head_age assets hhsize</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Which baseline variables predict response (for propensity or balancing; i. before a category variable)?</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. baseline variables of the propensity model or of the balancing (i. for categories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>classes</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>region urban</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Which variables define the weighting classes (for classes)?</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. class variables for nonresponse classes (UN 2008 section 6.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>region urban head_female agegrp</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Which Cells sheet columns define the cells (for post)?</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. cell variables for nonresponse post: the columns of the Cells sheet before total</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ngroups</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>How many propensity groups (10 = deciles)?</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 10 (command). propensity groups (deciles)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>moments</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Balance means only (1), also variances (2), also skewness (3)?</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 1 (command). balancing moments: 1 means, 2 adds variances, 3 adds skewness</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Should extreme weights be trimmed?</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: none. none | winsor | cap (HFPS Vol. 2 p. 11 winsorises at the 98th percentile; UN 2008 section 6.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>trim_pct</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>If winsor: at which percentile?</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 98 (command). winsorising percentile</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>trim_cap</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>If cap: at which value?</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. absolute cap for trim cap, or blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>trim_capmult</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>If cap: at how many times the median?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. cap as a multiple of the median, or blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>calibrate</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>rake</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Should the weights be calibrated to the Totals sheet?</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: none. none | rake | regress | post (Deville and Sarndal 1992; Deville, Sarndal and Sautory 1993)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cal_vars</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>region urban</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Which variables to calibrate on (blank = every variable on Totals)?</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. categorical variables to calibrate on; every category must be on the Totals sheet; blank = every variable there</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cal_ll</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Lower bound on the calibration ratio (regress), or blank?</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. lower bound on the weight ratio (regress), or blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cal_ul</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Upper bound, or blank?</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. upper bound, or blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>report_by</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Which variable should the report break the weights down by (blank = none)?</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. variable for the by-group table of the weighting report, or blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>report_files</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Write the Word method note and the Excel report?</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: yes. yes | no: write the Word method note and the Excel report into output_dir</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="37">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="seed" prompt="Which seed should every draw use (any whole number; keep it to repeat the draw)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: level, change (or leave blank for the default)" promptTitle="target" prompt="Is the sample sized to measure a level, or to detect a change?" type="list">
+      <formula1>"level,change"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="p" prompt="What share do you expect for the key indicator (0 to 1)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="relmargin" prompt="How precise, as a relative margin of error (0.10 = plus or minus 10 percent of the share)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="margin" prompt="Or as an absolute margin (0.03 = plus or minus 3 points)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="change" prompt="If a change: how large a change should be detected (-0.05 = a fall of 5 points)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="power" prompt="If a change: with what power (0.8 is usual)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="deff" prompt="How clustered is the sample (design effect; 2 for areas then households, 1 for a list)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="nonresponse_mult" prompt="How much to inflate for nonresponse (1.1 = 10 percent more)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="attrition" prompt="What share of the panel is lost each round (0.015 = 1.5 percent)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="rounds" prompt="How many rounds will the panel run?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="firstloss" prompt="What share is lost between the baseline and the first phone round?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="domains" prompt="For how many domains (regions, groups) is this precision needed?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="minsize" prompt="Below how many households is an area too small to sample alone (0 = no check)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="maxsize" prompt="Above how many households should an area be listed in segments (0 = no check)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="n_areas" prompt="How many areas should be selected in total?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: proportional, equal, neyman, power (or leave blank for the default)" promptTitle="allocation" prompt="How should the areas be spread across strata?" type="list">
+      <formula1>"proportional,equal,neyman,power"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="power_q" prompt="If power allocation: which exponent (0.5 is usual)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="min_areas" prompt="At least how many areas per stratum (0 = no minimum)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="max_areas" prompt="At most how many areas per stratum (0 = no maximum)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: ppssys, pps, systematic, srs, grid (or leave blank for the default)" promptTitle="stage1" prompt="How should the areas be drawn?" type="list">
+      <formula1>"ppssys,pps,systematic,srs,grid"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not allowed" error="A whole number, all, or 0" type="custom">
+      <formula1>OR(ISNUMBER(B30),B30="all")</formula1>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="households_per_area" prompt="How many households per selected area (blank = none; needs a household list or listing on Files)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="phone_per_psu" prompt="How many households per PSU are called first (blank = no phone subsample; needs a baseline on Files)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: yes, no (or leave blank for the default)" promptTitle="rdd" prompt="Should phone numbers be generated from operator prefixes (random digit dialing)?" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: baseline, probabilities (or leave blank for the default)" promptTitle="base_weight" prompt="Where does the base weight come from?" type="list">
+      <formula1>"baseline,probabilities"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: propensity, probit, classes, ebalance, ebalance_nobase, post, none (or leave blank for the default)" promptTitle="nonresponse" prompt="How should the weights be adjusted for households not interviewed?" type="list">
+      <formula1>"propensity,probit,classes,ebalance,ebalance_nobase,post,none"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="ngroups" prompt="How many propensity groups (10 = deciles)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="moments" prompt="Balance means only (1), also variances (2), also skewness (3)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: none, winsor, cap (or leave blank for the default)" promptTitle="trim" prompt="Should extreme weights be trimmed?" type="list">
+      <formula1>"none,winsor,cap"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_pct" prompt="If winsor: at which percentile?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_cap" prompt="If cap: at which value?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_capmult" prompt="If cap: at how many times the median?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: none, rake, regress, post (or leave blank for the default)" promptTitle="calibrate" prompt="Should the weights be calibrated to the Totals sheet?" type="list">
+      <formula1>"none,rake,regress,post"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="cal_ll" prompt="Lower bound on the calibration ratio (regress), or blank?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="cal_ul" prompt="Upper bound, or blank?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: yes, no (or leave blank for the default)" promptTitle="report_files" prompt="Write the Word method note and the Excel report?" type="list">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1503,22 +2123,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>stratum_id</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>population_hh</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>population_persons</t>
         </is>
@@ -1633,7 +2253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1655,52 +2275,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>area_id</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>stratum_id</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>size_hh</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>size_persons</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>urban</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>network</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>exclude</t>
         </is>
@@ -10907,11 +11527,26 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A5000">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(A2&lt;&gt;"",COUNTIF($A$2:$A$5000,A2)&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C5000">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>AND(A2&lt;&gt;"",OR(C2="",C2&lt;=0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="exclude is 0, 1 or blank" type="list">
+      <formula1>"0,1"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10926,17 +11561,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>total</t>
         </is>
@@ -11025,7 +11660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11042,27 +11677,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>urban</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>head_female</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>agegrp</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>total</t>
         </is>
@@ -11889,7 +12524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11904,17 +12539,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>prefix</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>n_numbers</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>digits</t>
         </is>
@@ -11958,7 +12593,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11982,62 +12617,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>psu</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>strata</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>probabilities</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>phone</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>area_id</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>round</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -12148,6 +12783,16 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(A2&lt;&gt;"",B2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="role is baseline, round, household_list or listing" prompt="baseline: the household file with weights; round: one file per phone round; household_list or listing: for the second stage" type="list">
+      <formula1>"baseline,round,household_list,listing"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/rtm_inputs.xlsx
+++ b/rtm_inputs.xlsx
@@ -902,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1556,441 +1556,463 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>segment_size</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Above how many households should a selected area be listed in segments (one segment chosen per area)?</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>default when blank: 150. households per listing segment: areas above it are listed in segments, one chosen at random per area (UN 2008 paras 138-140; 150 is a common field value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t># phone subsample of a baseline (rtmsample draw, reserve all)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>phone subsample of a baseline (rtmsample draw, reserve all)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>phone_per_psu</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>How many households per PSU are called first (blank = no phone subsample; needs a baseline on Files)?</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>blank = not used. households per PSU called first, every other household an ordered replacement; blank = none (needs a baseline row in Files)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t># random digit dialing (rtmsample rdd)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>random digit dialing (rtmsample rdd)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>rdd</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Should phone numbers be generated from operator prefixes (random digit dialing)?</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>default when blank: no. yes | no: draw numbers from the Prefixes sheet; the numbers are never exported</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t># weights of a round (rtmweight base, nonresponse, trim, calibrate, report)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>weights of a round (rtmweight base, nonresponse, trim, calibrate, report)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>base_weight</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>baseline</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Where does the base weight come from?</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>default when blank: baseline. baseline | probabilities: the baseline weight redistributed to the phone sample, or 1 / product of the probabilities (HFPS Vol. 2 pp. 10-11, 21)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nonresponse</t>
+          <t>base_weight</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>propensity</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>How should the weights be adjusted for households not interviewed?</t>
+          <t>Where does the base weight come from?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>default when blank: propensity. propensity | probit | classes | ebalance | ebalance_nobase | post | none (HFPS Vol. 2 Annex A2.3.1: propensity in deciles; ebalance and post are L2 program practice)</t>
+          <t>default when blank: baseline. baseline | probabilities: the baseline weight redistributed to the phone sample, or 1 / product of the probabilities (HFPS Vol. 2 pp. 10-11, 21)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>covariates</t>
+          <t>nonresponse</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>urban i.educ head_age assets hhsize</t>
+          <t>propensity</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Which baseline variables predict response (for propensity or balancing; i. before a category variable)?</t>
+          <t>How should the weights be adjusted for households not interviewed?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. baseline variables of the propensity model or of the balancing (i. for categories)</t>
+          <t>default when blank: propensity. propensity | probit | classes | ebalance | ebalance_nobase | post | none (HFPS Vol. 2 Annex A2.3.1: propensity in deciles; ebalance and post are L2 program practice)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>classes</t>
+          <t>covariates</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>region urban</t>
+          <t>urban i.educ head_age assets hhsize</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Which variables define the weighting classes (for classes)?</t>
+          <t>Which baseline variables predict response (for propensity or balancing; i. before a category variable)?</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. class variables for nonresponse classes (UN 2008 section 6.5)</t>
+          <t>blank = not used. baseline variables of the propensity model or of the balancing (i. for categories)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cells</t>
+          <t>classes</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>region urban head_female agegrp</t>
+          <t>region urban</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Which Cells sheet columns define the cells (for post)?</t>
+          <t>Which variables define the weighting classes (for classes)?</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. cell variables for nonresponse post: the columns of the Cells sheet before total</t>
+          <t>blank = not used. class variables for nonresponse classes (UN 2008 section 6.5)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ngroups</t>
+          <t>cells</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>region urban head_female agegrp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>How many propensity groups (10 = deciles)?</t>
+          <t>Which Cells sheet columns define the cells (for post)?</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>default when blank: 10 (command). propensity groups (deciles)</t>
+          <t>blank = not used. cell variables for nonresponse post: the columns of the Cells sheet before total</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>moments</t>
+          <t>ngroups</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Balance means only (1), also variances (2), also skewness (3)?</t>
+          <t>How many propensity groups (10 = deciles)?</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>default when blank: 1 (command). balancing moments: 1 means, 2 adds variances, 3 adds skewness</t>
+          <t>default when blank: 10 (command). propensity groups (deciles)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>trim</t>
+          <t>moments</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Should extreme weights be trimmed?</t>
+          <t>Balance means only (1), also variances (2), also skewness (3)?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>default when blank: none. none | winsor | cap (HFPS Vol. 2 p. 11 winsorises at the 98th percentile; UN 2008 section 6.8)</t>
+          <t>default when blank: 1 (command). balancing moments: 1 means, 2 adds variances, 3 adds skewness</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>trim_pct</t>
+          <t>trim</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>If winsor: at which percentile?</t>
+          <t>Should extreme weights be trimmed?</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>default when blank: 98 (command). winsorising percentile</t>
+          <t>default when blank: none. none | winsor | cap (HFPS Vol. 2 p. 11 winsorises at the 98th percentile; UN 2008 section 6.8)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>trim_cap</t>
+          <t>trim_pct</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>98</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>If cap: at which value?</t>
+          <t>If winsor: at which percentile?</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. absolute cap for trim cap, or blank</t>
+          <t>default when blank: 98 (command). winsorising percentile</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>trim_capmult</t>
+          <t>trim_cap</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>If cap: at how many times the median?</t>
+          <t>If cap: at which value?</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. cap as a multiple of the median, or blank</t>
+          <t>blank = not used. absolute cap for trim cap, or blank</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>calibrate</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>rake</t>
+          <t>trim_capmult</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Should the weights be calibrated to the Totals sheet?</t>
+          <t>If cap: at how many times the median?</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>default when blank: none. none | rake | regress | post (Deville and Sarndal 1992; Deville, Sarndal and Sautory 1993)</t>
+          <t>blank = not used. cap as a multiple of the median, or blank</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cal_vars</t>
+          <t>calibrate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>region urban</t>
+          <t>rake</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Which variables to calibrate on (blank = every variable on Totals)?</t>
+          <t>Should the weights be calibrated to the Totals sheet?</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. categorical variables to calibrate on; every category must be on the Totals sheet; blank = every variable there</t>
+          <t>default when blank: none. none | rake | regress | post (Deville and Sarndal 1992; Deville, Sarndal and Sautory 1993)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cal_ll</t>
+          <t>cal_vars</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>region urban</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lower bound on the calibration ratio (regress), or blank?</t>
+          <t>Which variables to calibrate on (blank = every variable on Totals)?</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. lower bound on the weight ratio (regress), or blank</t>
+          <t>blank = not used. categorical variables to calibrate on; every category must be on the Totals sheet; blank = every variable there</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cal_ul</t>
+          <t>cal_ll</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Upper bound, or blank?</t>
+          <t>Lower bound on the calibration ratio (regress), or blank?</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. upper bound, or blank</t>
+          <t>blank = not used. lower bound on the weight ratio (regress), or blank</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>report_by</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>region</t>
+          <t>cal_ul</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Which variable should the report break the weights down by (blank = none)?</t>
+          <t>Upper bound, or blank?</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>blank = not used. variable for the by-group table of the weighting report, or blank</t>
+          <t>blank = not used. upper bound, or blank</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>report_by</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Which variable should the report break the weights down by (blank = none)?</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>blank = not used. variable for the by-group table of the weighting report, or blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>report_files</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Write the Word method note and the Excel report?</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>default when blank: yes. yes | no: write the Word method note and the Excel report into output_dir</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="37">
+  <dataValidations count="38">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="seed" prompt="Which seed should every draw use (any whole number; keep it to repeat the draw)?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
@@ -2060,46 +2082,49 @@
     <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="households_per_area" prompt="How many households per selected area (blank = none; needs a household list or listing on Files)?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="phone_per_psu" prompt="How many households per PSU are called first (blank = no phone subsample; needs a baseline on Files)?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="segment_size" prompt="Above how many households should a selected area be listed in segments (one segment chosen per area)?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: yes, no (or leave blank for the default)" promptTitle="rdd" prompt="Should phone numbers be generated from operator prefixes (random digit dialing)?" type="list">
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="phone_per_psu" prompt="How many households per PSU are called first (blank = no phone subsample; needs a baseline on Files)?" type="decimal" operator="greaterThanOrEqual">
+      <formula1>-1000000000</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: yes, no (or leave blank for the default)" promptTitle="rdd" prompt="Should phone numbers be generated from operator prefixes (random digit dialing)?" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: baseline, probabilities (or leave blank for the default)" promptTitle="base_weight" prompt="Where does the base weight come from?" type="list">
+    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: baseline, probabilities (or leave blank for the default)" promptTitle="base_weight" prompt="Where does the base weight come from?" type="list">
       <formula1>"baseline,probabilities"</formula1>
     </dataValidation>
-    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: propensity, probit, classes, ebalance, ebalance_nobase, post, none (or leave blank for the default)" promptTitle="nonresponse" prompt="How should the weights be adjusted for households not interviewed?" type="list">
+    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: propensity, probit, classes, ebalance, ebalance_nobase, post, none (or leave blank for the default)" promptTitle="nonresponse" prompt="How should the weights be adjusted for households not interviewed?" type="list">
       <formula1>"propensity,probit,classes,ebalance,ebalance_nobase,post,none"</formula1>
     </dataValidation>
-    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="ngroups" prompt="How many propensity groups (10 = deciles)?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="ngroups" prompt="How many propensity groups (10 = deciles)?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="moments" prompt="Balance means only (1), also variances (2), also skewness (3)?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="moments" prompt="Balance means only (1), also variances (2), also skewness (3)?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: none, winsor, cap (or leave blank for the default)" promptTitle="trim" prompt="Should extreme weights be trimmed?" type="list">
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: none, winsor, cap (or leave blank for the default)" promptTitle="trim" prompt="Should extreme weights be trimmed?" type="list">
       <formula1>"none,winsor,cap"</formula1>
     </dataValidation>
-    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_pct" prompt="If winsor: at which percentile?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_pct" prompt="If winsor: at which percentile?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_cap" prompt="If cap: at which value?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_cap" prompt="If cap: at which value?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_capmult" prompt="If cap: at how many times the median?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="trim_capmult" prompt="If cap: at how many times the median?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: none, rake, regress, post (or leave blank for the default)" promptTitle="calibrate" prompt="Should the weights be calibrated to the Totals sheet?" type="list">
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: none, rake, regress, post (or leave blank for the default)" promptTitle="calibrate" prompt="Should the weights be calibrated to the Totals sheet?" type="list">
       <formula1>"none,rake,regress,post"</formula1>
     </dataValidation>
-    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="cal_ll" prompt="Lower bound on the calibration ratio (regress), or blank?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="cal_ll" prompt="Lower bound on the calibration ratio (regress), or blank?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="cal_ul" prompt="Upper bound, or blank?" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not a number" error="This row needs a number (or blank for the default)" promptTitle="cal_ul" prompt="Upper bound, or blank?" type="decimal" operator="greaterThanOrEqual">
       <formula1>-1000000000</formula1>
     </dataValidation>
-    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: yes, no (or leave blank for the default)" promptTitle="report_files" prompt="Write the Word method note and the Excel report?" type="list">
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not an allowed value" error="Choose one of: yes, no (or leave blank for the default)" promptTitle="report_files" prompt="Write the Word method note and the Excel report?" type="list">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
